--- a/GS_쏠비치양양_프로모션_품의.xlsx
+++ b/GS_쏠비치양양_프로모션_품의.xlsx
@@ -777,7 +777,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>147~252</t>
+          <t>69~118</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>147~252</t>
+          <t>69~118</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>112~440</t>
+          <t>290~440</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>-191~137</t>
+          <t>116~137</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>147~267</t>
+          <t>69~118</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>230~542</t>
+          <t>359~558</t>
         </is>
       </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>-191~137</t>
+          <t>116~137</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>147~279</t>
+          <t>78~130</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>147~279</t>
+          <t>78~130</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>147~294</t>
+          <t>78~130</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>147~294</t>
+          <t>78~130</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>130~279</t>
+          <t>78~130</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>130~279</t>
+          <t>78~130</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>130~294</t>
+          <t>78~130</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>130~294</t>
+          <t>78~130</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>130~294</t>
+          <t>78~130</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
